--- a/data/yes24/daily/20260830_yes24_it_bestseller.xlsx
+++ b/data/yes24/daily/20260830_yes24_it_bestseller.xlsx
@@ -5137,7 +5137,7 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="J30" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K30" s="4" t="s">
         <x:v>18</x:v>
